--- a/artfynd/A 40987-2022 artfynd.xlsx
+++ b/artfynd/A 40987-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40987-2022 artfynd.xlsx
+++ b/artfynd/A 40987-2022 artfynd.xlsx
@@ -675,50 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2010757</v>
+        <v>16502591</v>
       </c>
       <c r="B2" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storberget, NO Renfors, 11 km VNV om Boliden k:a, Vb</t>
+          <t>Bergtjärnen, Renström, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743770.3748518451</v>
+        <v>743921</v>
       </c>
       <c r="R2" t="n">
-        <v>7207045.768790389</v>
+        <v>7207201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,48 +768,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>skuggad av barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>på sydvänd liten bergbrant</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Lill Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1935248</v>
+        <v>2010757</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743770.3748518451</v>
+        <v>743770</v>
       </c>
       <c r="R3" t="n">
-        <v>7207045.768790389</v>
+        <v>7207046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2009-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,64 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16502591</v>
+        <v>1935248</v>
       </c>
       <c r="B4" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Renström, Vb</t>
+          <t>Storberget, NO Renfors, 11 km VNV om Boliden k:a, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743921.2496509692</v>
+        <v>743770</v>
       </c>
       <c r="R4" t="n">
-        <v>7207200.523764389</v>
+        <v>7207046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,22 +978,36 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>skuggad av barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på sydvänd liten bergbrant</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40987-2022 artfynd.xlsx
+++ b/artfynd/A 40987-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16502591</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2010757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,8 +1023,18 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1935248</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>